--- a/files/config.xlsx
+++ b/files/config.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\Tool\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tgodoi01\Downloads\lixo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A0863A-4BBE-4AA0-9BFD-F5C2D1E06DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD07ACBD-A701-4471-9158-34CC158F4AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,15 +33,6 @@
     <t>Network [Path]</t>
   </si>
   <si>
-    <t>C:\Projetos\Tool\files\Cópia de Cópia de Controle CR'S _ DCN's (version 7).xlsx</t>
-  </si>
-  <si>
-    <t>C:\Projetos\Tool\files\codigo_ucs.xlsx</t>
-  </si>
-  <si>
-    <t>C:\Projetos\Tool\files\Lista Mestra de Validações e Aplicadores_Rev2.xlsx</t>
-  </si>
-  <si>
     <t>Id name</t>
   </si>
   <si>
@@ -54,27 +45,15 @@
     <t>lista_app</t>
   </si>
   <si>
-    <t>C:\Projetos\Tool\files\Circuitos_Especiais.xlsx</t>
-  </si>
-  <si>
     <t>circuitos_especiais</t>
   </si>
   <si>
     <t>terminais_sem</t>
   </si>
   <si>
-    <t>C:\Projetos\Tool\files\Terminais_SEM.xlsx</t>
-  </si>
-  <si>
-    <t>C:\Projetos\Tool\files\Cabos_SEM.xlsx</t>
-  </si>
-  <si>
     <t>Lista_de_cabos</t>
   </si>
   <si>
-    <t>C:\Projetos\Tool\files\Aplicadores de Selo Rev. 09-11-2019.xlsm</t>
-  </si>
-  <si>
     <t>calhas_de_selos</t>
   </si>
   <si>
@@ -90,28 +69,49 @@
     <t>G:\Lead Prep Engeneering\14-Die Center\Aplicadores de Selo Rev. 09-11-2019.xlsm</t>
   </si>
   <si>
-    <t>C:\Projetos\Tool\files\Lista Mestra Validações USCAR45 e GMW17136 (Nova Base - 27-0-2024)).xlsx</t>
-  </si>
-  <si>
     <t>Take_Rates</t>
   </si>
   <si>
-    <t>C:\Projetos\Tool\files\Take_Rates.xlsx</t>
-  </si>
-  <si>
     <t>G:\Lead Prep Engeneering\06-Validações\00 - Lista Mestra de Validações e Aplicadores\Lista Mestra Validações USCAR45 e GMW17136 (Nova Base - 27-0-2024)).xlsx</t>
   </si>
   <si>
     <t>mapa_aloc_corte</t>
   </si>
   <si>
-    <t>C:\Projetos\Tool\files\Mapa Geral de Alocações de Circuitos e processos Rev 19 - 22-09-2025.xlsm</t>
-  </si>
-  <si>
     <t>Lista_de_cabos_com_legacy</t>
   </si>
   <si>
-    <t>C:\Projetos\Tool\files\Lista_de_Cabos_Com_Legacy.xlsx</t>
+    <t>C:\Tooling_Engineering\files\codigo_ucs.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Tooling_Engineering\files\Cópia de Cópia de Controle CR'S _ DCN's (version 7).xlsx</t>
+  </si>
+  <si>
+    <t>C:\Tooling_Engineering\files\Lista Mestra de Validações e Aplicadores_Rev2.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Tooling_Engineering\files\Circuitos_Especiais.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Tooling_Engineering\files\Terminais_SEM.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Tooling_Engineering\files\Cabos_SEM.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Tooling_Engineering\files\Aplicadores de Selo Rev. 09-11-2019.xlsm</t>
+  </si>
+  <si>
+    <t>C:\Tooling_Engineering\files\Lista Mestra Validações USCAR45 e GMW17136 (Nova Base - 27-0-2024)).xlsx</t>
+  </si>
+  <si>
+    <t>C:\Tooling_Engineering\files\Take_Rates.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Tooling_Engineering\files\Mapa Geral de Alocações de Circuitos e processos Rev 19 - 22-09-2025.xlsm</t>
+  </si>
+  <si>
+    <t>C:\Tooling_Engineering\files\Lista_de_Cabos_Com_Legacy.xlsx</t>
   </si>
 </sst>
 </file>
@@ -453,7 +453,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -464,99 +464,99 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
